--- a/reports/telegram/aegis_daily_2026-08-04.xlsx
+++ b/reports/telegram/aegis_daily_2026-08-04.xlsx
@@ -833,7 +833,7 @@
       </c>
       <c r="AM2" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04 06:52</t>
+          <t>2026-08-04 07:19</t>
         </is>
       </c>
     </row>
@@ -962,7 +962,7 @@
       </c>
       <c r="AM3" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04 06:52</t>
+          <t>2026-08-04 07:19</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="AM4" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04 06:52</t>
+          <t>2026-08-04 07:19</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="AM5" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04 06:52</t>
+          <t>2026-08-04 07:19</t>
         </is>
       </c>
     </row>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="AM6" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04 06:52</t>
+          <t>2026-08-04 07:19</t>
         </is>
       </c>
     </row>
@@ -1460,7 +1460,7 @@
       </c>
       <c r="AM7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04 06:52</t>
+          <t>2026-08-04 07:19</t>
         </is>
       </c>
     </row>
@@ -1587,7 +1587,7 @@
       </c>
       <c r="AM8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04 06:52</t>
+          <t>2026-08-04 07:19</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AM9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04 06:52</t>
+          <t>2026-08-04 07:19</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="AM10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04 06:52</t>
+          <t>2026-08-04 07:19</t>
         </is>
       </c>
     </row>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="AM11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04 06:52</t>
+          <t>2026-08-04 07:19</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="AM12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04 06:52</t>
+          <t>2026-08-04 07:19</t>
         </is>
       </c>
     </row>
@@ -2230,7 +2230,7 @@
       </c>
       <c r="AM13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04 06:52</t>
+          <t>2026-08-04 07:19</t>
         </is>
       </c>
     </row>
@@ -2363,7 +2363,7 @@
       </c>
       <c r="AM14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04 06:52</t>
+          <t>2026-08-04 07:19</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="AM15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04 06:52</t>
+          <t>2026-08-04 07:19</t>
         </is>
       </c>
     </row>
@@ -2621,7 +2621,7 @@
       </c>
       <c r="AM16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04 06:52</t>
+          <t>2026-08-04 07:19</t>
         </is>
       </c>
     </row>
@@ -2746,7 +2746,7 @@
       </c>
       <c r="AM17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04 06:52</t>
+          <t>2026-08-04 07:19</t>
         </is>
       </c>
     </row>
@@ -2871,7 +2871,7 @@
       </c>
       <c r="AM18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04 06:52</t>
+          <t>2026-08-04 07:19</t>
         </is>
       </c>
     </row>
@@ -2996,7 +2996,7 @@
       </c>
       <c r="AM19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04 06:52</t>
+          <t>2026-08-04 07:19</t>
         </is>
       </c>
     </row>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="AM20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04 06:52</t>
+          <t>2026-08-04 07:19</t>
         </is>
       </c>
     </row>
@@ -3246,7 +3246,7 @@
       </c>
       <c r="AM21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04 06:52</t>
+          <t>2026-08-04 07:19</t>
         </is>
       </c>
     </row>
@@ -3367,7 +3367,7 @@
       </c>
       <c r="AM22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04 06:52</t>
+          <t>2026-08-04 07:19</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="AM23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04 06:52</t>
+          <t>2026-08-04 07:19</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3617,7 @@
       </c>
       <c r="AM24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04 06:52</t>
+          <t>2026-08-04 07:19</t>
         </is>
       </c>
     </row>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="AM25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04 06:52</t>
+          <t>2026-08-04 07:19</t>
         </is>
       </c>
     </row>
@@ -3869,7 +3869,7 @@
       </c>
       <c r="AM26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04 06:52</t>
+          <t>2026-08-04 07:19</t>
         </is>
       </c>
     </row>
@@ -3998,7 +3998,7 @@
       </c>
       <c r="AM27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04 06:52</t>
+          <t>2026-08-04 07:19</t>
         </is>
       </c>
     </row>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="AM28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04 06:52</t>
+          <t>2026-08-04 07:19</t>
         </is>
       </c>
     </row>
@@ -4268,7 +4268,7 @@
       </c>
       <c r="AM29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04 06:52</t>
+          <t>2026-08-04 07:19</t>
         </is>
       </c>
     </row>
@@ -4403,7 +4403,7 @@
       </c>
       <c r="AM30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04 06:52</t>
+          <t>2026-08-04 07:19</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="AM31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04 06:52</t>
+          <t>2026-08-04 07:19</t>
         </is>
       </c>
     </row>
@@ -4673,7 +4673,7 @@
       </c>
       <c r="AM32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04 06:52</t>
+          <t>2026-08-04 07:19</t>
         </is>
       </c>
     </row>
@@ -4808,7 +4808,7 @@
       </c>
       <c r="AM33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04 06:52</t>
+          <t>2026-08-04 07:19</t>
         </is>
       </c>
     </row>
@@ -4943,7 +4943,7 @@
       </c>
       <c r="AM34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04 06:52</t>
+          <t>2026-08-04 07:19</t>
         </is>
       </c>
     </row>
@@ -5078,7 +5078,7 @@
       </c>
       <c r="AM35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04 06:52</t>
+          <t>2026-08-04 07:19</t>
         </is>
       </c>
     </row>
@@ -5213,7 +5213,7 @@
       </c>
       <c r="AM36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04 06:52</t>
+          <t>2026-08-04 07:19</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="AM37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04 06:52</t>
+          <t>2026-08-04 07:19</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="AM38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04 06:52</t>
+          <t>2026-08-04 07:19</t>
         </is>
       </c>
     </row>
@@ -5618,7 +5618,7 @@
       </c>
       <c r="AM39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04 06:52</t>
+          <t>2026-08-04 07:19</t>
         </is>
       </c>
     </row>
@@ -5753,7 +5753,7 @@
       </c>
       <c r="AM40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04 06:52</t>
+          <t>2026-08-04 07:19</t>
         </is>
       </c>
     </row>
